--- a/data/trans_dic/P6904-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,67; 47,62</t>
+          <t>24,01; 48,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,58; 56,74</t>
+          <t>29,54; 58,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,43; 59,04</t>
+          <t>28,9; 59,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,16; 60,62</t>
+          <t>30,84; 61,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,33; 48,52</t>
+          <t>21,24; 49,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,47; 53,18</t>
+          <t>20,92; 52,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,07; 65,77</t>
+          <t>36,45; 65,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,25; 59,05</t>
+          <t>36,81; 58,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,29; 44,52</t>
+          <t>27,03; 44,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,09; 50,78</t>
+          <t>30,99; 50,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,91; 57,0</t>
+          <t>36,48; 57,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,37; 55,68</t>
+          <t>37,64; 55,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,37; 38,22</t>
+          <t>11,08; 39,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,75; 65,97</t>
+          <t>33,0; 67,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,08; 71,3</t>
+          <t>33,7; 72,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,04; 56,79</t>
+          <t>27,22; 54,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,02; 59,91</t>
+          <t>30,51; 59,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 44,72</t>
+          <t>6,99; 43,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,14; 79,22</t>
+          <t>44,84; 80,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,65; 59,59</t>
+          <t>34,02; 62,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 44,7</t>
+          <t>23,52; 44,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,03; 52,45</t>
+          <t>25,64; 51,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,13; 71,86</t>
+          <t>43,86; 71,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,91; 54,31</t>
+          <t>34,0; 54,12</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,31; 73,83</t>
+          <t>54,78; 73,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,69; 64,02</t>
+          <t>40,77; 63,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,74; 68,51</t>
+          <t>45,01; 69,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,0; 76,35</t>
+          <t>50,11; 75,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,49; 80,47</t>
+          <t>29,62; 76,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,38; 76,64</t>
+          <t>41,35; 75,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,64; 100,0</t>
+          <t>36,13; 90,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61,58; 93,4</t>
+          <t>59,55; 92,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,4; 72,54</t>
+          <t>53,63; 72,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,36; 64,78</t>
+          <t>44,73; 63,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47,61; 72,19</t>
+          <t>47,1; 70,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,33; 77,06</t>
+          <t>56,47; 77,02</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,49; 65,66</t>
+          <t>52,11; 67,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,62; 71,21</t>
+          <t>54,35; 71,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,26; 72,55</t>
+          <t>56,41; 72,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,13; 76,02</t>
+          <t>57,84; 75,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,17; 71,68</t>
+          <t>43,78; 70,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,05; 68,73</t>
+          <t>43,62; 68,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,04; 80,68</t>
+          <t>61,25; 80,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,1; 69,59</t>
+          <t>53,16; 69,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,22; 64,75</t>
+          <t>51,93; 64,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,47; 66,95</t>
+          <t>52,82; 67,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60,86; 73,65</t>
+          <t>60,67; 73,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,84; 70,53</t>
+          <t>58,78; 70,69</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,43; 62,12</t>
+          <t>36,42; 61,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,38; 72,68</t>
+          <t>41,59; 72,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,54; 75,76</t>
+          <t>50,86; 75,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,35; 88,44</t>
+          <t>64,06; 88,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,13; 74,66</t>
+          <t>49,42; 73,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,29; 84,1</t>
+          <t>52,8; 82,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,56; 86,91</t>
+          <t>61,8; 87,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,02; 92,2</t>
+          <t>71,59; 91,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,05; 64,94</t>
+          <t>46,98; 65,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51,68; 74,75</t>
+          <t>52,78; 74,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,88; 76,95</t>
+          <t>60,02; 77,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,29; 89,64</t>
+          <t>72,41; 89,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -1417,221 +1417,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,09; 56,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,14; 60,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,09; 65,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,66; 66,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,96; 58,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,95; 58,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,93; 73,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,21; 75,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,28; 55,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,26; 58,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,47; 66,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,57; 69,96</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>52,24%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>54,83%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>59,55%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>61,49%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65,49%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>52,08%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>53,57%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>62,48%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>47,36; 56,78</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>49,21; 60,81</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>54,1; 64,93</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>55,63; 67,07</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>45,5; 59,0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,37; 58,36</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,83; 73,65</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>59,54; 74,43</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>48,19; 55,86</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>49,01; 58,03</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>58,35; 66,58</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>59,49; 69,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
@@ -1647,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15404; 30994</t>
+          <t>15628; 31524</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16403; 31467</t>
+          <t>16385; 32344</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13805; 27699</t>
+          <t>13556; 28008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13817; 27774</t>
+          <t>14128; 28195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9952; 22637</t>
+          <t>9911; 23088</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9372; 22176</t>
+          <t>8724; 21816</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16569; 30211</t>
+          <t>16741; 30006</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21491; 35009</t>
+          <t>21826; 34776</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28260; 49747</t>
+          <t>30200; 49827</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29236; 49333</t>
+          <t>30105; 49069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33339; 52922</t>
+          <t>33874; 53282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39280; 58523</t>
+          <t>39564; 58545</t>
         </is>
       </c>
     </row>
@@ -2135,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4817; 16188</t>
+          <t>4691; 16546</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10891; 23367</t>
+          <t>11690; 24007</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10606; 21559</t>
+          <t>10189; 21778</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13729; 28836</t>
+          <t>13822; 27880</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12909; 24932</t>
+          <t>12696; 24887</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2005; 11902</t>
+          <t>1861; 11567</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12974; 23287</t>
+          <t>13180; 23733</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13766; 25122</t>
+          <t>14341; 26358</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19890; 37531</t>
+          <t>19753; 37537</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15527; 32540</t>
+          <t>15908; 31824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26909; 42848</t>
+          <t>26155; 42822</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32445; 50476</t>
+          <t>31601; 50297</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54327; 73855</t>
+          <t>54800; 73337</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33091; 50816</t>
+          <t>32360; 50683</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29928; 45828</t>
+          <t>30109; 46733</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28679; 44685</t>
+          <t>29328; 43974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4477; 13106</t>
+          <t>4824; 12506</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13955; 25844</t>
+          <t>13944; 25419</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3410; 9569</t>
+          <t>3458; 8700</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10985; 16662</t>
+          <t>10622; 16494</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63272; 84378</t>
+          <t>62379; 83875</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51303; 73266</t>
+          <t>50585; 72091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36403; 55193</t>
+          <t>36011; 53759</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42253; 58846</t>
+          <t>43122; 58811</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>103401; 131857</t>
+          <t>104644; 134807</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61765; 82029</t>
+          <t>62612; 82401</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77003; 99303</t>
+          <t>77211; 99769</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76102; 101277</t>
+          <t>77054; 100930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22062; 35801</t>
+          <t>21865; 34978</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30615; 46706</t>
+          <t>29639; 46561</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51318; 67834</t>
+          <t>51494; 67765</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55098; 73594</t>
+          <t>56219; 73507</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130964; 162374</t>
+          <t>130225; 160967</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>96096; 122615</t>
+          <t>96747; 123713</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>134464; 162736</t>
+          <t>134049; 162066</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>138218; 168559</t>
+          <t>140470; 168938</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2618,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23959; 39763</t>
+          <t>23313; 39656</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15754; 29073</t>
+          <t>16636; 28838</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35612; 52348</t>
+          <t>35139; 52072</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32929; 45254</t>
+          <t>32780; 45501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33550; 48993</t>
+          <t>32432; 48256</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24145; 36724</t>
+          <t>23055; 36131</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29607; 41129</t>
+          <t>29245; 41251</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>90370; 117318</t>
+          <t>91093; 116698</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>62288; 84181</t>
+          <t>60898; 84452</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43242; 62546</t>
+          <t>44165; 62038</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69715; 89586</t>
+          <t>69872; 90622</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>128978; 159932</t>
+          <t>129197; 160390</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2831,62 +2690,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>294</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>269</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2758,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>246734</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178441</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113916</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110383</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145362</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>230727</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360650</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353802</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>439501</t>
         </is>
       </c>
     </row>
@@ -2967,282 +2826,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>222390; 267606</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>159921; 196372</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>189315; 228223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>188962; 227403</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>98975; 128347</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96046; 125458</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>131790; 158949</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>212098; 265034</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>334291; 387206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>265561; 316514</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>331123; 377794</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>412105; 483970</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>246734</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>178441</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>208440</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>208774</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>113916</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>110383</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>230727</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>360650</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>288825</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>353802</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>439501</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>223693; 268198</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>160143; 197915</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>189336; 227259</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>188867; 227692</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100160; 129872</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>94801; 124703</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>131567; 159313</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>209752; 262226</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>333659; 386773</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>264194; 312849</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>330461; 377016</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>411545; 478538</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3252,7 +2903,6 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P6904-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,01; 48,44</t>
+          <t>25,3; 48,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,54; 58,32</t>
+          <t>29,75; 58,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,9; 59,7</t>
+          <t>29,3; 59,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,84; 61,54</t>
+          <t>29,72; 58,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 49,49</t>
+          <t>21,1; 48,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,92; 52,31</t>
+          <t>21,92; 53,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,45; 65,32</t>
+          <t>35,52; 65,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,81; 58,65</t>
+          <t>36,22; 57,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,03; 44,59</t>
+          <t>26,62; 44,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,99; 50,5</t>
+          <t>30,56; 50,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,48; 57,39</t>
+          <t>35,93; 58,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,64; 55,7</t>
+          <t>36,82; 54,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,08; 39,06</t>
+          <t>10,8; 38,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,0; 67,78</t>
+          <t>32,25; 66,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,7; 72,03</t>
+          <t>35,41; 73,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,22; 54,9</t>
+          <t>26,12; 55,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,51; 59,8</t>
+          <t>30,83; 59,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 43,46</t>
+          <t>7,79; 46,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,84; 80,74</t>
+          <t>42,8; 80,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,02; 62,52</t>
+          <t>34,98; 61,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,52; 44,7</t>
+          <t>24,1; 44,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,64; 51,3</t>
+          <t>25,18; 51,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,86; 71,81</t>
+          <t>45,23; 71,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,0; 54,12</t>
+          <t>34,12; 54,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,78; 73,32</t>
+          <t>54,75; 73,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,77; 63,86</t>
+          <t>41,28; 64,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,01; 69,86</t>
+          <t>44,49; 69,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,11; 75,14</t>
+          <t>52,0; 77,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 76,79</t>
+          <t>30,21; 77,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,35; 75,38</t>
+          <t>43,17; 77,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,13; 90,92</t>
+          <t>27,42; 90,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59,55; 92,46</t>
+          <t>59,94; 92,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,63; 72,11</t>
+          <t>53,83; 72,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,73; 63,74</t>
+          <t>45,25; 64,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47,1; 70,31</t>
+          <t>47,49; 70,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,47; 77,02</t>
+          <t>57,44; 78,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,11; 67,13</t>
+          <t>51,9; 65,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,35; 71,53</t>
+          <t>53,46; 71,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,41; 72,89</t>
+          <t>55,47; 72,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,84; 75,76</t>
+          <t>60,57; 77,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,78; 70,03</t>
+          <t>45,21; 72,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,62; 68,52</t>
+          <t>43,59; 68,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,25; 80,6</t>
+          <t>60,6; 80,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,16; 69,5</t>
+          <t>52,38; 68,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,93; 64,19</t>
+          <t>52,61; 64,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,82; 67,55</t>
+          <t>52,59; 67,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60,67; 73,35</t>
+          <t>61,33; 73,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,78; 70,69</t>
+          <t>59,5; 71,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,42; 61,95</t>
+          <t>37,2; 62,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,59; 72,09</t>
+          <t>40,09; 72,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,86; 75,36</t>
+          <t>52,88; 75,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,06; 88,92</t>
+          <t>68,96; 89,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,42; 73,54</t>
+          <t>50,13; 74,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,8; 82,74</t>
+          <t>55,29; 83,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,8; 87,17</t>
+          <t>62,63; 86,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,59; 91,71</t>
+          <t>64,53; 79,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46,98; 65,15</t>
+          <t>46,62; 64,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52,78; 74,14</t>
+          <t>52,95; 74,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60,02; 77,84</t>
+          <t>60,48; 77,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,41; 89,9</t>
+          <t>69,89; 81,94</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,26%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,09; 56,66</t>
+          <t>47,51; 57,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49,14; 60,34</t>
+          <t>48,93; 61,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,09; 65,21</t>
+          <t>54,02; 65,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55,66; 66,98</t>
+          <t>57,69; 68,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,96; 58,31</t>
+          <t>44,66; 58,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,95; 58,72</t>
+          <t>44,7; 58,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,93; 73,49</t>
+          <t>60,78; 73,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,21; 75,23</t>
+          <t>56,78; 65,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48,28; 55,92</t>
+          <t>48,48; 56,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49,26; 58,71</t>
+          <t>49,01; 58,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58,47; 66,71</t>
+          <t>58,22; 66,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59,57; 69,96</t>
+          <t>58,56; 66,04</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20584</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48662</t>
+          <t>52112</t>
         </is>
       </c>
     </row>
@@ -1786,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15628; 31524</t>
+          <t>16466; 31772</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16385; 32344</t>
+          <t>16498; 32199</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13556; 28008</t>
+          <t>13745; 28050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14128; 28195</t>
+          <t>15464; 30556</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9911; 23088</t>
+          <t>9842; 22711</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8724; 21816</t>
+          <t>9143; 22325</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16741; 30006</t>
+          <t>16318; 30077</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21826; 34776</t>
+          <t>22469; 35774</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30200; 49827</t>
+          <t>29745; 50028</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30105; 49069</t>
+          <t>29690; 49080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33874; 53282</t>
+          <t>33357; 54363</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39564; 58545</t>
+          <t>42003; 61859</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20937</t>
+          <t>20897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>21727</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41136</t>
+          <t>42625</t>
         </is>
       </c>
     </row>
@@ -1994,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4691; 16546</t>
+          <t>4574; 16241</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11690; 24007</t>
+          <t>11424; 23458</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10189; 21778</t>
+          <t>10706; 22302</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13822; 27880</t>
+          <t>13597; 28707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12696; 24887</t>
+          <t>12831; 24871</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1861; 11567</t>
+          <t>2074; 12335</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13180; 23733</t>
+          <t>12582; 23518</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14341; 26358</t>
+          <t>15898; 27973</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19753; 37537</t>
+          <t>20237; 37644</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15908; 31824</t>
+          <t>15621; 32203</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26155; 42822</t>
+          <t>26972; 42661</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31601; 50297</t>
+          <t>33272; 52938</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37313</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51603</t>
+          <t>56098</t>
         </is>
       </c>
     </row>
@@ -2202,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54800; 73337</t>
+          <t>54762; 73556</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32360; 50683</t>
+          <t>32764; 51360</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30109; 46733</t>
+          <t>29761; 46412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29328; 43974</t>
+          <t>31971; 47626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4824; 12506</t>
+          <t>4920; 12638</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13944; 25419</t>
+          <t>14557; 26078</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3458; 8700</t>
+          <t>2623; 8685</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10622; 16494</t>
+          <t>12261; 18910</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62379; 83875</t>
+          <t>62607; 83750</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50585; 72091</t>
+          <t>51169; 73188</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36011; 53759</t>
+          <t>36313; 54196</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43122; 58811</t>
+          <t>47068; 63920</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89951</t>
+          <t>106104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65115</t>
+          <t>69650</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>155065</t>
+          <t>175754</t>
         </is>
       </c>
     </row>
@@ -2410,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>104644; 134807</t>
+          <t>104221; 131928</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62612; 82401</t>
+          <t>61589; 81934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77211; 99769</t>
+          <t>75916; 99050</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77054; 100930</t>
+          <t>93140; 119605</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21865; 34978</t>
+          <t>22581; 36000</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29639; 46561</t>
+          <t>29620; 46415</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51494; 67765</t>
+          <t>50947; 67853</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56219; 73507</t>
+          <t>59591; 78404</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130225; 160967</t>
+          <t>131938; 161149</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>96747; 123713</t>
+          <t>96320; 124403</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>134049; 162066</t>
+          <t>135509; 162657</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>140470; 168938</t>
+          <t>159176; 191636</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39991</t>
+          <t>53334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>103044</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>143034</t>
+          <t>126892</t>
         </is>
       </c>
     </row>
@@ -2618,62 +2618,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23313; 39656</t>
+          <t>23813; 40097</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16636; 28838</t>
+          <t>16037; 28886</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35139; 52072</t>
+          <t>36540; 52215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32780; 45501</t>
+          <t>45286; 58537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32432; 48256</t>
+          <t>32898; 48729</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23055; 36131</t>
+          <t>24144; 36426</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29245; 41251</t>
+          <t>29640; 41152</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91093; 116698</t>
+          <t>65593; 80646</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60898; 84452</t>
+          <t>60440; 84211</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44165; 62038</t>
+          <t>44305; 62668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69872; 90622</t>
+          <t>70412; 90429</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>129197; 160390</t>
+          <t>116934; 137094</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208774</t>
+          <t>243557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>230727</t>
+          <t>209924</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>439501</t>
+          <t>453480</t>
         </is>
       </c>
     </row>
@@ -2826,62 +2826,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>222390; 267606</t>
+          <t>224382; 270196</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>159921; 196372</t>
+          <t>159251; 199040</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189315; 228223</t>
+          <t>189080; 228492</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>188962; 227403</t>
+          <t>222094; 262984</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>98975; 128347</t>
+          <t>98303; 128383</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>96046; 125458</t>
+          <t>95508; 124256</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>131790; 158949</t>
+          <t>131465; 158442</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>212098; 265034</t>
+          <t>194953; 226578</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>334291; 387206</t>
+          <t>335689; 388595</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>265561; 316514</t>
+          <t>264213; 314778</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>331123; 377794</t>
+          <t>329707; 377060</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>412105; 483970</t>
+          <t>426539; 480996</t>
         </is>
       </c>
     </row>
